--- a/gng2.xlsx
+++ b/gng2.xlsx
@@ -44,7 +44,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,11 @@
         <fgColor rgb="00234E70"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -99,6 +104,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,7 +453,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14.85546875" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -1115,7 +1123,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="8"/>
@@ -1185,9 +1193,9 @@
           <t>succeeded</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Failed: already registered or group closed</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -1227,9 +1235,9 @@
           <t>succeeded</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Failed: already registered or group closed</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -1269,9 +1277,9 @@
           <t>succeeded</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Failed: already registered or group closed</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -1311,9 +1319,9 @@
           <t>succeeded</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Failed: already registered or group closed</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -1353,9 +1361,9 @@
           <t>succeeded</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Failed: يوجد تعارض في وقت المحاضرة النظري ، من فضلك راجع جدول الطالب</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
